--- a/data/inventory_logs.xlsx
+++ b/data/inventory_logs.xlsx
@@ -1,25 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sibale\Desktop\Flask FarmManagementSystem\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="27">
   <si>
     <t>Date</t>
   </si>
@@ -60,6 +55,9 @@
     <t>MSMA</t>
   </si>
   <si>
+    <t>Urea Fertilizer</t>
+  </si>
+  <si>
     <t>DG01001</t>
   </si>
   <si>
@@ -75,26 +73,38 @@
     <t>DG22000</t>
   </si>
   <si>
+    <t>Itimu</t>
+  </si>
+  <si>
     <t>Top dressing</t>
   </si>
   <si>
+    <t>DG23000</t>
+  </si>
+  <si>
     <t>Replenishment</t>
   </si>
   <si>
     <t>Issued (via request)</t>
   </si>
   <si>
+    <t>Issued</t>
+  </si>
+  <si>
     <t>admin</t>
+  </si>
+  <si>
+    <t>atambala</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -158,14 +168,6 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -212,7 +214,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -244,10 +246,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -279,7 +280,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -455,22 +455,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.7109375" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I14"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -499,9 +488,9 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9">
       <c r="A2" s="2">
-        <v>45828.798387569441</v>
+        <v>45828.79838756944</v>
       </c>
       <c r="B2" t="s">
         <v>11</v>
@@ -510,15 +499,15 @@
         <v>200</v>
       </c>
       <c r="D2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" s="2">
-        <v>45828.800000682873</v>
+        <v>45828.80000068287</v>
       </c>
       <c r="B3" t="s">
         <v>11</v>
@@ -527,15 +516,15 @@
         <v>150</v>
       </c>
       <c r="D3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" s="2">
-        <v>45828.800533657413</v>
+        <v>45828.80053365741</v>
       </c>
       <c r="B4" t="s">
         <v>11</v>
@@ -544,10 +533,10 @@
         <v>100</v>
       </c>
       <c r="D4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5" s="2">
         <v>45828.80245398148</v>
       </c>
@@ -558,10 +547,10 @@
         <v>80</v>
       </c>
       <c r="D5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6" s="2">
         <v>45828.80275224537</v>
       </c>
@@ -572,12 +561,12 @@
         <v>50</v>
       </c>
       <c r="D6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7" s="2">
-        <v>45828.804933784719</v>
+        <v>45828.80493378472</v>
       </c>
       <c r="B7" t="s">
         <v>12</v>
@@ -586,12 +575,12 @@
         <v>50</v>
       </c>
       <c r="D7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
       <c r="A8" s="2">
-        <v>45828.805222233786</v>
+        <v>45828.80522223379</v>
       </c>
       <c r="B8" t="s">
         <v>12</v>
@@ -600,15 +589,15 @@
         <v>200</v>
       </c>
       <c r="D8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9" s="2">
         <v>45828.83156997685</v>
       </c>
       <c r="F9" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G9" t="s">
         <v>11</v>
@@ -617,12 +606,12 @@
         <v>200</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9">
       <c r="A10" s="2">
-        <v>45828.831979189818</v>
+        <v>45828.83197918982</v>
       </c>
       <c r="F10" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G10" t="s">
         <v>12</v>
@@ -631,7 +620,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -639,16 +628,16 @@
         <v>11</v>
       </c>
       <c r="F11" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H11">
         <v>200</v>
       </c>
       <c r="I11" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -656,13 +645,53 @@
         <v>12</v>
       </c>
       <c r="F12" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H12">
         <v>10</v>
       </c>
       <c r="I12" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" s="2">
+        <v>45853.84380373843</v>
+      </c>
+      <c r="B13" t="s">
+        <v>13</v>
+      </c>
+      <c r="F13" t="s">
+        <v>22</v>
+      </c>
+      <c r="H13">
+        <v>20</v>
+      </c>
+      <c r="I13" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" s="2">
+        <v>45853.84403695917</v>
+      </c>
+      <c r="B14" t="s">
+        <v>13</v>
+      </c>
+      <c r="D14" t="s">
+        <v>19</v>
+      </c>
+      <c r="E14" t="s">
         <v>21</v>
+      </c>
+      <c r="F14" t="s">
+        <v>24</v>
+      </c>
+      <c r="H14">
+        <v>198</v>
+      </c>
+      <c r="I14" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>

--- a/data/inventory_logs.xlsx
+++ b/data/inventory_logs.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="31">
   <si>
     <t>Date</t>
   </si>
@@ -76,10 +76,22 @@
     <t>Itimu</t>
   </si>
   <si>
+    <t>Growers</t>
+  </si>
+  <si>
     <t>Top dressing</t>
   </si>
   <si>
     <t>DG23000</t>
+  </si>
+  <si>
+    <t>Top dressing F26</t>
+  </si>
+  <si>
+    <t>SR#06968</t>
+  </si>
+  <si>
+    <t>DSC</t>
   </si>
   <si>
     <t>Replenishment</t>
@@ -456,7 +468,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:9">
@@ -502,7 +514,7 @@
         <v>14</v>
       </c>
       <c r="E2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -519,7 +531,7 @@
         <v>15</v>
       </c>
       <c r="E3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -597,7 +609,7 @@
         <v>45828.83156997685</v>
       </c>
       <c r="F9" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="G9" t="s">
         <v>11</v>
@@ -611,7 +623,7 @@
         <v>45828.83197918982</v>
       </c>
       <c r="F10" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="G10" t="s">
         <v>12</v>
@@ -628,13 +640,13 @@
         <v>11</v>
       </c>
       <c r="F11" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="H11">
         <v>200</v>
       </c>
       <c r="I11" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -645,13 +657,13 @@
         <v>12</v>
       </c>
       <c r="F12" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="H12">
         <v>10</v>
       </c>
       <c r="I12" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -662,18 +674,18 @@
         <v>13</v>
       </c>
       <c r="F13" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H13">
         <v>20</v>
       </c>
       <c r="I13" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="2">
-        <v>45853.84403695917</v>
+        <v>45853.84403695602</v>
       </c>
       <c r="B14" t="s">
         <v>13</v>
@@ -682,16 +694,82 @@
         <v>19</v>
       </c>
       <c r="E14" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F14" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="H14">
         <v>198</v>
       </c>
       <c r="I14" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" s="2">
+        <v>45883.77947631945</v>
+      </c>
+      <c r="B15" t="s">
+        <v>13</v>
+      </c>
+      <c r="D15" t="s">
+        <v>19</v>
+      </c>
+      <c r="E15" t="s">
+        <v>23</v>
+      </c>
+      <c r="F15" t="s">
+        <v>28</v>
+      </c>
+      <c r="H15">
+        <v>20</v>
+      </c>
+      <c r="I15" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" s="2">
+        <v>45883.78121310185</v>
+      </c>
+      <c r="B16" t="s">
+        <v>13</v>
+      </c>
+      <c r="D16" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" t="s">
+        <v>24</v>
+      </c>
+      <c r="F16" t="s">
+        <v>28</v>
+      </c>
+      <c r="H16">
+        <v>15</v>
+      </c>
+      <c r="I16" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" s="2">
+        <v>45883.78203775001</v>
+      </c>
+      <c r="B17" t="s">
+        <v>13</v>
+      </c>
+      <c r="E17" t="s">
+        <v>25</v>
+      </c>
+      <c r="F17" t="s">
         <v>26</v>
+      </c>
+      <c r="H17">
+        <v>1500</v>
+      </c>
+      <c r="I17" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/data/inventory_logs.xlsx
+++ b/data/inventory_logs.xlsx
@@ -1,20 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sibale\Desktop\Flask FarmManagementSystem\data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12000"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="24">
   <si>
     <t>Date</t>
   </si>
@@ -22,101 +27,77 @@
     <t>ItemName</t>
   </si>
   <si>
-    <t>QuantityIssued</t>
-  </si>
-  <si>
-    <t>IssuedTo</t>
-  </si>
-  <si>
     <t>Remarks</t>
   </si>
   <si>
     <t>Action</t>
   </si>
   <si>
-    <t>Item</t>
-  </si>
-  <si>
     <t>Quantity</t>
   </si>
   <si>
-    <t>PerformedBy</t>
-  </si>
-  <si>
-    <t>2025-06-20 22:02</t>
-  </si>
-  <si>
-    <t>2025-06-20 22:33</t>
-  </si>
-  <si>
-    <t>UREA</t>
-  </si>
-  <si>
-    <t>MSMA</t>
-  </si>
-  <si>
-    <t>Urea Fertilizer</t>
-  </si>
-  <si>
-    <t>DG01001</t>
-  </si>
-  <si>
-    <t>DG20000</t>
-  </si>
-  <si>
-    <t>DG30000</t>
-  </si>
-  <si>
-    <t>DG14000</t>
-  </si>
-  <si>
-    <t>DG22000</t>
-  </si>
-  <si>
-    <t>Itimu</t>
-  </si>
-  <si>
-    <t>Growers</t>
-  </si>
-  <si>
-    <t>Top dressing</t>
-  </si>
-  <si>
-    <t>DG23000</t>
-  </si>
-  <si>
-    <t>Top dressing F26</t>
-  </si>
-  <si>
-    <t>SR#06968</t>
-  </si>
-  <si>
-    <t>DSC</t>
-  </si>
-  <si>
-    <t>Replenishment</t>
-  </si>
-  <si>
-    <t>Issued (via request)</t>
+    <t>SR#</t>
+  </si>
+  <si>
+    <t>Collector</t>
+  </si>
+  <si>
+    <t>Department</t>
+  </si>
+  <si>
+    <t>PassOutNo</t>
+  </si>
+  <si>
+    <t>IssuedBy</t>
+  </si>
+  <si>
+    <t>2026-03-10 23:21</t>
+  </si>
+  <si>
+    <t>A6 HARDCOVER BOOK</t>
   </si>
   <si>
     <t>Issued</t>
   </si>
   <si>
-    <t>admin</t>
+    <t>SR1773182751</t>
+  </si>
+  <si>
+    <t>Kossam</t>
+  </si>
+  <si>
+    <t>Agriculture</t>
+  </si>
+  <si>
+    <t>PO-4177-202603102321</t>
   </si>
   <si>
     <t>atambala</t>
+  </si>
+  <si>
+    <t>2026-03-10 23:22</t>
+  </si>
+  <si>
+    <t>ANALYSIS PAD 7 COLLUM</t>
+  </si>
+  <si>
+    <t>SR1773183274</t>
+  </si>
+  <si>
+    <t>Biasi</t>
+  </si>
+  <si>
+    <t>Administration</t>
+  </si>
+  <si>
+    <t>PO-7492-202603102322</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
-  </numFmts>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -127,10 +108,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -168,18 +146,25 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -467,11 +452,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I17"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:J3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.140625" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.140625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -499,280 +493,69 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="2">
-        <v>45828.79838756944</v>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>10</v>
       </c>
       <c r="B2" t="s">
         <v>11</v>
       </c>
-      <c r="C2">
-        <v>200</v>
-      </c>
       <c r="D2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" t="s">
         <v>14</v>
       </c>
-      <c r="E2" t="s">
+      <c r="H2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G3" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="3" spans="1:9">
-      <c r="A3" s="2">
-        <v>45828.80000068287</v>
-      </c>
-      <c r="B3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3">
-        <v>150</v>
-      </c>
-      <c r="D3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
-      <c r="A4" s="2">
-        <v>45828.80053365741</v>
-      </c>
-      <c r="B4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4">
-        <v>100</v>
-      </c>
-      <c r="D4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
-      <c r="A5" s="2">
-        <v>45828.80245398148</v>
-      </c>
-      <c r="B5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5">
-        <v>80</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="H3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J3" t="s">
         <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
-      <c r="A6" s="2">
-        <v>45828.80275224537</v>
-      </c>
-      <c r="B6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6">
-        <v>50</v>
-      </c>
-      <c r="D6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9">
-      <c r="A7" s="2">
-        <v>45828.80493378472</v>
-      </c>
-      <c r="B7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7">
-        <v>50</v>
-      </c>
-      <c r="D7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9">
-      <c r="A8" s="2">
-        <v>45828.80522223379</v>
-      </c>
-      <c r="B8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8">
-        <v>200</v>
-      </c>
-      <c r="D8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9">
-      <c r="A9" s="2">
-        <v>45828.83156997685</v>
-      </c>
-      <c r="F9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G9" t="s">
-        <v>11</v>
-      </c>
-      <c r="H9">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9">
-      <c r="A10" s="2">
-        <v>45828.83197918982</v>
-      </c>
-      <c r="F10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G10" t="s">
-        <v>12</v>
-      </c>
-      <c r="H10">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9">
-      <c r="A11" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11" t="s">
-        <v>11</v>
-      </c>
-      <c r="F11" t="s">
-        <v>27</v>
-      </c>
-      <c r="H11">
-        <v>200</v>
-      </c>
-      <c r="I11" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9">
-      <c r="A12" t="s">
-        <v>10</v>
-      </c>
-      <c r="B12" t="s">
-        <v>12</v>
-      </c>
-      <c r="F12" t="s">
-        <v>27</v>
-      </c>
-      <c r="H12">
-        <v>10</v>
-      </c>
-      <c r="I12" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9">
-      <c r="A13" s="2">
-        <v>45853.84380373843</v>
-      </c>
-      <c r="B13" t="s">
-        <v>13</v>
-      </c>
-      <c r="F13" t="s">
-        <v>26</v>
-      </c>
-      <c r="H13">
-        <v>20</v>
-      </c>
-      <c r="I13" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9">
-      <c r="A14" s="2">
-        <v>45853.84403695602</v>
-      </c>
-      <c r="B14" t="s">
-        <v>13</v>
-      </c>
-      <c r="D14" t="s">
-        <v>19</v>
-      </c>
-      <c r="E14" t="s">
-        <v>22</v>
-      </c>
-      <c r="F14" t="s">
-        <v>28</v>
-      </c>
-      <c r="H14">
-        <v>198</v>
-      </c>
-      <c r="I14" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9">
-      <c r="A15" s="2">
-        <v>45883.77947631945</v>
-      </c>
-      <c r="B15" t="s">
-        <v>13</v>
-      </c>
-      <c r="D15" t="s">
-        <v>19</v>
-      </c>
-      <c r="E15" t="s">
-        <v>23</v>
-      </c>
-      <c r="F15" t="s">
-        <v>28</v>
-      </c>
-      <c r="H15">
-        <v>20</v>
-      </c>
-      <c r="I15" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9">
-      <c r="A16" s="2">
-        <v>45883.78121310185</v>
-      </c>
-      <c r="B16" t="s">
-        <v>13</v>
-      </c>
-      <c r="D16" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" t="s">
-        <v>24</v>
-      </c>
-      <c r="F16" t="s">
-        <v>28</v>
-      </c>
-      <c r="H16">
-        <v>15</v>
-      </c>
-      <c r="I16" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9">
-      <c r="A17" s="2">
-        <v>45883.78203775001</v>
-      </c>
-      <c r="B17" t="s">
-        <v>13</v>
-      </c>
-      <c r="E17" t="s">
-        <v>25</v>
-      </c>
-      <c r="F17" t="s">
-        <v>26</v>
-      </c>
-      <c r="H17">
-        <v>1500</v>
-      </c>
-      <c r="I17" t="s">
-        <v>29</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/inventory_logs.xlsx
+++ b/data/inventory_logs.xlsx
@@ -1,119 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sibale\Desktop\Flask FarmManagementSystem\data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12000"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="24">
-  <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>ItemName</t>
-  </si>
-  <si>
-    <t>Remarks</t>
-  </si>
-  <si>
-    <t>Action</t>
-  </si>
-  <si>
-    <t>Quantity</t>
-  </si>
-  <si>
-    <t>SR#</t>
-  </si>
-  <si>
-    <t>Collector</t>
-  </si>
-  <si>
-    <t>Department</t>
-  </si>
-  <si>
-    <t>PassOutNo</t>
-  </si>
-  <si>
-    <t>IssuedBy</t>
-  </si>
-  <si>
-    <t>2026-03-10 23:21</t>
-  </si>
-  <si>
-    <t>A6 HARDCOVER BOOK</t>
-  </si>
-  <si>
-    <t>Issued</t>
-  </si>
-  <si>
-    <t>SR1773182751</t>
-  </si>
-  <si>
-    <t>Kossam</t>
-  </si>
-  <si>
-    <t>Agriculture</t>
-  </si>
-  <si>
-    <t>PO-4177-202603102321</t>
-  </si>
-  <si>
-    <t>atambala</t>
-  </si>
-  <si>
-    <t>2026-03-10 23:22</t>
-  </si>
-  <si>
-    <t>ANALYSIS PAD 7 COLLUM</t>
-  </si>
-  <si>
-    <t>SR1773183274</t>
-  </si>
-  <si>
-    <t>Biasi</t>
-  </si>
-  <si>
-    <t>Administration</t>
-  </si>
-  <si>
-    <t>PO-7492-202603102322</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -128,43 +46,93 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -452,107 +420,206 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.140625" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="21.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.140625" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>ItemName</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Remarks</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>SR#</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Collector</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Department</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>PassOutNo</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>IssuedBy</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-03-10 23:21</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>A6 HARDCOVER BOOK</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Issued</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>SR1773182751</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Kossam</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>PO-4177-202603102321</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>atambala</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2">
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-03-10 23:22</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ANALYSIS PAD 7 COLLUM</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Issued</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
         <v>1</v>
       </c>
-      <c r="F2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I2" t="s">
-        <v>16</v>
-      </c>
-      <c r="J2" t="s">
-        <v>17</v>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>SR1773183274</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Biasi</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Administration</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>PO-7492-202603102322</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>atambala</t>
+        </is>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3">
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-03-12 10:25</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>SURF 1kg pocket</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Collected </t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Issued</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
         <v>1</v>
       </c>
-      <c r="F3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I3" t="s">
-        <v>23</v>
-      </c>
-      <c r="J3" t="s">
-        <v>17</v>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>SR1773303862</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Cedrick January</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>PO-6486-202603121024</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>atambala</t>
+        </is>
       </c>
     </row>
   </sheetData>
